--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045423</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL26</t>
+    <t>20045422</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L28</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,7 +28,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
+    <t>PT,(E-3B)</t>
   </si>
   <si>
     <t>20137023</t>
@@ -43,130 +43,112 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20135747</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAP XL24</t>
+    <t>20136706</t>
+  </si>
+  <si>
+    <t>IDM BABY DPRS L28</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
-  </si>
-  <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10015650</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
-  </si>
-  <si>
-    <t>20137940</t>
-  </si>
-  <si>
-    <t>VICKS BABY BALM 20G</t>
+    <t>20035629</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+VNL BOX350</t>
+  </si>
+  <si>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 350</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20037413</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 90</t>
+    <t>20122091</t>
+  </si>
+  <si>
+    <t>KAHF FC.SCRB G/E 100</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10020713</t>
+  </si>
+  <si>
+    <t>WG COCO CUBE CP 1KG</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10021003</t>
+  </si>
+  <si>
+    <t>W/COCO CCPD SLC 1KG</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
+  </si>
+  <si>
+    <t>20136510</t>
+  </si>
+  <si>
+    <t>MILO 3IN1 ACT-GO 400</t>
+  </si>
+  <si>
+    <t>20113913</t>
+  </si>
+  <si>
+    <t>MY/B WIPES ANTBC 2'S</t>
+  </si>
+  <si>
+    <t>10010805</t>
+  </si>
+  <si>
+    <t>SANIA MNYK GR PCH 2L</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20125041</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLS LV90</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
-  </si>
-  <si>
-    <t>20070380</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN PCS</t>
-  </si>
-  <si>
-    <t>PT,(E-2H)</t>
-  </si>
-  <si>
-    <t>20046368</t>
-  </si>
-  <si>
-    <t>KURMA DATE CROWN 250</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL900</t>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
   </si>
 </sst>
 </file>
@@ -559,14 +541,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -666,15 +648,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -683,18 +665,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -703,18 +685,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -726,15 +708,15 @@
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -746,15 +728,15 @@
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -766,15 +748,15 @@
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -783,30 +765,30 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -820,133 +802,93 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
